--- a/artfynd/A 18515-2024 artfynd.xlsx
+++ b/artfynd/A 18515-2024 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>117659351</v>
       </c>
       <c r="B2" t="n">
-        <v>97755</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -725,7 +720,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Älgstan (Älgstan), Vstm</t>
+          <t>Älgstan, Älgstan, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -809,12 +804,7 @@
         <v>117659545</v>
       </c>
       <c r="B3" t="n">
-        <v>96799</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97989</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -851,7 +841,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Älgstan (Älgstan), Vstm</t>
+          <t>Älgstan, Älgstan, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
@@ -935,12 +925,7 @@
         <v>117659173</v>
       </c>
       <c r="B4" t="n">
-        <v>96793</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -977,7 +962,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Älgstan (Älgstan), Vstm</t>
+          <t>Älgstan, Älgstan, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
